--- a/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>LVWR</t>
   </si>
@@ -656,113 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44829</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44738</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44647</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44465</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E8" s="3">
         <v>8100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7000</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -772,41 +775,44 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E9" s="3">
         <v>7100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
@@ -816,41 +822,44 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-3000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-1800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
@@ -860,8 +869,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +890,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +935,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +982,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -998,20 +1017,23 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1076,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1094,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E17" s="3">
         <v>33500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>39000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>32700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>37400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>35700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>31900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1200</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-25400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-32000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-24900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-28200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-21000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-17100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1200</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,25 +1207,26 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>10800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
@@ -1202,58 +1235,61 @@
         <v>100</v>
       </c>
       <c r="K20" s="3">
+        <v>100</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>19600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-18800</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-13100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-40000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-20500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-21300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-20000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-18200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1263,13 +1299,16 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1284,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1307,52 +1346,58 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-40700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-21900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-19500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-17200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>19300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-20100</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1360,19 +1405,19 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
@@ -1381,7 +1426,7 @@
         <v>100</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1395,8 +1440,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1487,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-40700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-21800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-19800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-20100</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-40700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20100</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,25 +1769,28 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
@@ -1730,69 +1799,75 @@
         <v>-100</v>
       </c>
       <c r="K32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-19600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>18800</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-40700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-21800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20100</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1910,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-40700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-21800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20100</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44829</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44738</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44647</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44465</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2049,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>167900</v>
+      </c>
+      <c r="E41" s="3">
         <v>199900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>215900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>236000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>265200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>1200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1700</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,40 +2141,43 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E43" s="3">
         <v>5200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2096,40 +2188,43 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E44" s="3">
         <v>32800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>32200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>31100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>29200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>33600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>25800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17700</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2140,96 +2235,105 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>600</v>
       </c>
       <c r="P45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>210700</v>
+      </c>
+      <c r="E46" s="3">
         <v>239900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>255900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>272800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>301900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>140500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>39400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>42400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>1700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2261,51 +2365,54 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>400200</v>
+        <v>0</v>
       </c>
       <c r="N47" s="3">
         <v>400200</v>
       </c>
       <c r="O47" s="3">
+        <v>400200</v>
+      </c>
+      <c r="P47" s="3">
         <v>400100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E48" s="3">
         <v>39900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22700</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2316,40 +2423,43 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E49" s="3">
         <v>9800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10500</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2360,8 +2470,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,40 +2564,43 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E52" s="3">
         <v>6300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -2492,8 +2611,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2658,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>266100</v>
+      </c>
+      <c r="E54" s="3">
         <v>295900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>310500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>325800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>351800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>182400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>76900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>75800</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>401900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>402200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>402300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,35 +2745,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E57" s="3">
         <v>25500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2660,8 +2790,11 @@
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2674,8 +2807,8 @@
       <c r="F58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2684,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>12300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2704,96 +2837,105 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E59" s="3">
         <v>19900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>116600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>29600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>47100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E60" s="3">
         <v>45400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>40800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>134300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>40700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>29600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2816,11 +2958,11 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>5800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2836,40 +2978,43 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E62" s="3">
         <v>12000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>13100</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>13100</v>
@@ -2877,11 +3022,14 @@
       <c r="O62" s="3">
         <v>13100</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3166,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E66" s="3">
         <v>57400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>61300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>38300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>139900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>39000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>42700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>40700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>60200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,26 +3420,29 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-132000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-98900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-84300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-43600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-22400</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3282,20 +3455,23 @@
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-3000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-57900</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3608,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>205900</v>
+      </c>
+      <c r="E76" s="3">
         <v>238500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>249100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>287500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>306800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>42500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>37900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22900</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N76" s="3">
         <v>359200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>361400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>342100</v>
       </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3702,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44829</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44738</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44647</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44465</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-40700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-21800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20100</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,16 +3822,17 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1400</v>
-      </c>
-      <c r="E83" s="3">
-        <v>700</v>
       </c>
       <c r="F83" s="3">
         <v>700</v>
@@ -3643,23 +3841,23 @@
         <v>700</v>
       </c>
       <c r="H83" s="3">
+        <v>700</v>
+      </c>
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1300</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -3669,8 +3867,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4102,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-16600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-24600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-25500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-26500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,41 +4170,42 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-3200</v>
       </c>
       <c r="I91" s="3">
         <v>-3200</v>
       </c>
       <c r="J91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -3995,8 +4215,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,41 +4309,44 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5200</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-3200</v>
       </c>
       <c r="I94" s="3">
         <v>-3200</v>
       </c>
       <c r="J94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3800</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -4127,8 +4356,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4422,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,41 +4563,44 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1600</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>193700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>126600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>15300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>30700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>24100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>18700</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -4365,8 +4610,11 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4409,48 +4657,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-20200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-29200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>163100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>96800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>LVWR</t>
   </si>
@@ -656,119 +656,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44829</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44738</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44647</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E8" s="3">
         <v>15100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7000</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
@@ -778,44 +782,47 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E9" s="3">
         <v>20300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8800</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
@@ -825,44 +832,47 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-5200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-3000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-1800</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
@@ -872,8 +882,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,8 +904,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -938,8 +952,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1002,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1020,20 +1040,23 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1079,8 +1102,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E17" s="3">
         <v>48800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>39000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>32700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>37400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>35700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>31900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>32800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1200</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-33700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-25400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-32000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-24900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-28200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-21000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-17100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,28 +1241,29 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
@@ -1238,61 +1272,64 @@
         <v>100</v>
       </c>
       <c r="L20" s="3">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>19600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-30100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-40000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-20500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-21300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-20000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-14200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1302,16 +1339,19 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1326,19 +1366,19 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>100</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1349,55 +1389,61 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-33100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-40700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-21100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-21900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-20900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>19300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1408,19 +1454,19 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
@@ -1429,7 +1475,7 @@
         <v>100</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1443,8 +1489,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-33100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-40700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-21100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-21800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-19600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-19800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-33100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-40700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-19600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-19800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,28 +1839,31 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
@@ -1802,72 +1872,78 @@
         <v>-100</v>
       </c>
       <c r="L32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-19600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>18800</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-33100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-40700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-21100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-19600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-19800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-33100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-40700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-21100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-19600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-19800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44829</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44738</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44647</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,55 +2136,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E41" s="3">
         <v>167900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>199900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>215900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>236000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>265200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11900</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3">
         <v>1200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1700</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2144,43 +2234,46 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E43" s="3">
         <v>7700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9800</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2191,43 +2284,46 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E44" s="3">
         <v>32100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>32800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>32200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>31100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>29200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>33600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>25800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17700</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2238,102 +2334,111 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E45" s="3">
         <v>3000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>600</v>
       </c>
       <c r="Q45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>182400</v>
+      </c>
+      <c r="E46" s="3">
         <v>210700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>239900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>255900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>272800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>301900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>140500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>42400</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O46" s="3">
         <v>1700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2368,54 +2473,57 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
-        <v>400200</v>
+        <v>0</v>
       </c>
       <c r="O47" s="3">
         <v>400200</v>
       </c>
       <c r="P47" s="3">
+        <v>400200</v>
+      </c>
+      <c r="Q47" s="3">
         <v>400100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E48" s="3">
         <v>39600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22700</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2426,43 +2534,46 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E49" s="3">
         <v>9700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10500</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2473,8 +2584,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,43 +2684,46 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E52" s="3">
         <v>6200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -2614,8 +2734,11 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>237100</v>
+      </c>
+      <c r="E54" s="3">
         <v>266100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>295900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>310500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>325800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>351800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>182400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>76900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>75800</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>401900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>402200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>402300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,38 +2876,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E57" s="3">
         <v>26300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2793,22 +2924,25 @@
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2820,16 +2954,16 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>12300</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2840,102 +2974,111 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E59" s="3">
         <v>20000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>116600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>29600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>47100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E60" s="3">
         <v>46300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>45400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>40800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>134300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40700</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>29600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>47100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2961,11 +3104,11 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>5800</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2981,43 +3124,46 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E62" s="3">
         <v>14000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
-        <v>13100</v>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O62" s="3">
         <v>13100</v>
@@ -3025,11 +3171,14 @@
       <c r="P62" s="3">
         <v>13100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E66" s="3">
         <v>60300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>61300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>38300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>45000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>139900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>39000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>42700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>40700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>60200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,29 +3594,32 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-155600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-132000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-98900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-84300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-43600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-22400</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3458,20 +3632,23 @@
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-3000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-57900</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E76" s="3">
         <v>205900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>238500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>249100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>287500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>306800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>42500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>37900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22900</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>359200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>361400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>342100</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44829</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44738</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44647</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-33100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-40700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-21100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-19600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-19800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,19 +4021,20 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E83" s="3">
         <v>3000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>700</v>
       </c>
       <c r="G83" s="3">
         <v>700</v>
@@ -3844,23 +4043,23 @@
         <v>700</v>
       </c>
       <c r="I83" s="3">
+        <v>700</v>
+      </c>
+      <c r="J83" s="3">
         <v>900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1300</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -3870,8 +4069,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-27600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-24600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-25500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-26500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-18600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,44 +4391,45 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-3200</v>
       </c>
       <c r="J91" s="3">
         <v>-3200</v>
       </c>
       <c r="K91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="L91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3800</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -4218,8 +4439,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,44 +4539,47 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5200</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-3200</v>
       </c>
       <c r="J94" s="3">
         <v>-3200</v>
       </c>
       <c r="K94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="L94" s="3">
         <v>-2500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3800</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -4359,8 +4589,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4425,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,44 +4809,47 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>193700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>126600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>15300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>30700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>24100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>18700</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -4613,8 +4859,11 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4660,51 +4909,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-32000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-29200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>163100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>96800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>LVWR</t>
   </si>
@@ -656,126 +656,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44829</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44738</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44647</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E8" s="3">
         <v>5000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7000</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
@@ -785,47 +789,50 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E9" s="3">
         <v>9100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8800</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
@@ -835,47 +842,50 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-4100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-5200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-3000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-1800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
@@ -885,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1043,20 +1063,23 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E17" s="3">
         <v>35400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>33500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>39000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>32700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>37400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>35700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>31900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-30400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-33700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-25400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-32000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-24900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-21000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-17100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1200</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,31 +1275,32 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>6800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1275,64 +1309,67 @@
         <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>19600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-18800</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-30100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-40000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-20500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-21300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-14200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-15800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1342,8 +1379,11 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1353,8 +1393,8 @@
       <c r="E22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1369,19 +1409,19 @@
         <v>0</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>300</v>
-      </c>
-      <c r="M22" s="3">
-        <v>100</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1392,58 +1432,64 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-33100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-21100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-21900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-20900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-17200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>19300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20100</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1457,19 +1503,19 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
@@ -1478,7 +1524,7 @@
         <v>100</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1492,8 +1538,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-33100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-40700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-21100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-21800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-20900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-19600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-19800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20100</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-33100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-40700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-21800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-17200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20100</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,31 +1909,34 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -1875,75 +1945,81 @@
         <v>-100</v>
       </c>
       <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>18800</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-33100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-40700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-21800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-20900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-17200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20100</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-33100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-40700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-21800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-20900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-17200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20100</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44829</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44738</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44647</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,58 +2223,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E41" s="3">
         <v>141000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>167900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>199900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>215900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>236000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>265200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11900</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3">
         <v>1200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,46 +2327,49 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E43" s="3">
         <v>3100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9800</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2287,46 +2380,49 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E44" s="3">
         <v>35100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>32100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>32800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>32200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>31100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>29200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>33600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>25800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>17700</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2337,108 +2433,117 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>600</v>
       </c>
       <c r="R45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>151500</v>
+      </c>
+      <c r="E46" s="3">
         <v>182400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>210700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>239900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>255900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>272800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>301900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>140500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>39400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>42400</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3">
         <v>1700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2476,57 +2581,60 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
-        <v>400200</v>
+        <v>0</v>
       </c>
       <c r="P47" s="3">
         <v>400200</v>
       </c>
       <c r="Q47" s="3">
+        <v>400200</v>
+      </c>
+      <c r="R47" s="3">
         <v>400100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E48" s="3">
         <v>39200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>39900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>36100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22700</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -2537,46 +2645,49 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E49" s="3">
         <v>9600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10500</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -2587,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2696,37 +2816,37 @@
         <v>5900</v>
       </c>
       <c r="E52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F52" s="3">
         <v>6200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>204900</v>
+      </c>
+      <c r="E54" s="3">
         <v>237100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>266100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>295900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>310500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>325800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>351800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>182400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>76900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>75800</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3">
         <v>401900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>402200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>402300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,41 +3007,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E57" s="3">
         <v>27500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>25500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>22400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11400</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2927,8 +3058,11 @@
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2957,16 +3091,16 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>12300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2977,108 +3111,117 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E59" s="3">
         <v>16700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>19900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>116600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>29600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>47100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E60" s="3">
         <v>44100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>46300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>45400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>40800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>134300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P60" s="3">
         <v>29600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>27600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>47100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3107,11 +3250,11 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>5800</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3127,46 +3270,49 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E62" s="3">
         <v>9200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>12000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6300</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>13100</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P62" s="3">
         <v>13100</v>
@@ -3174,11 +3320,14 @@
       <c r="Q62" s="3">
         <v>13100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E66" s="3">
         <v>53300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>61300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>38300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>139900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>39000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P66" s="3">
         <v>42700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>60200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,32 +3768,35 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-180400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-155600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-132000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-98900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-84300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-43600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-22400</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3635,20 +3809,23 @@
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>-3000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-57900</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E76" s="3">
         <v>183800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>205900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>238500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>249100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>287500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>306800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>42500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22900</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P76" s="3">
         <v>359200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>361400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>342100</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44829</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44738</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44647</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-33100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-40700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-21800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-20900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-17200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20100</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,22 +4220,23 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E83" s="3">
         <v>2300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>700</v>
       </c>
       <c r="H83" s="3">
         <v>700</v>
@@ -4046,23 +4245,23 @@
         <v>700</v>
       </c>
       <c r="J83" s="3">
+        <v>700</v>
+      </c>
+      <c r="K83" s="3">
         <v>900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -4072,8 +4271,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-27600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-25500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-18600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-22800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,47 +4612,48 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-3200</v>
       </c>
       <c r="K91" s="3">
         <v>-3200</v>
       </c>
       <c r="L91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3800</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -4442,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,47 +4769,50 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5200</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-3200</v>
       </c>
       <c r="K94" s="3">
         <v>-3200</v>
       </c>
       <c r="L94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="M94" s="3">
         <v>-2500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3800</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -4592,8 +4822,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,47 +5055,50 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>193700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>126600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>15300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>30700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>24100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>18700</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -4862,8 +5108,11 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4912,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-26900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-32000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-20200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-29200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>163100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>96800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>LVWR</t>
   </si>
@@ -656,133 +656,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44829</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44738</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44647</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E8" s="3">
         <v>6400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7000</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
@@ -792,50 +796,53 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8800</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
@@ -845,50 +852,53 @@
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-4100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-5200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L10" s="3">
         <v>1000</v>
       </c>
-      <c r="H10" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
@@ -898,8 +908,11 @@
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -933,8 +947,8 @@
       <c r="F12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
+      <c r="G12" s="3">
+        <v>54100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>4</v>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,31 +1042,34 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>2500</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1066,43 +1086,46 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E17" s="3">
         <v>34600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>39000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>32700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>26100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-28200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-30400</v>
       </c>
-      <c r="F18" s="3">
-        <v>-33700</v>
-      </c>
       <c r="G18" s="3">
-        <v>-25400</v>
+        <v>-33800</v>
       </c>
       <c r="H18" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-32000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-24900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-28200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-21000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-19900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-17100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1200</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,34 +1309,35 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3400</v>
+        <v>-2600</v>
       </c>
       <c r="E20" s="3">
-        <v>6800</v>
+        <v>-1800</v>
       </c>
       <c r="F20" s="3">
-        <v>700</v>
+        <v>-4800</v>
       </c>
       <c r="G20" s="3">
-        <v>10800</v>
+        <v>1700</v>
       </c>
       <c r="H20" s="3">
-        <v>-8700</v>
+        <v>-8000</v>
       </c>
       <c r="I20" s="3">
-        <v>3700</v>
+        <v>11400</v>
       </c>
       <c r="J20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K20" s="3">
         <v>6300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
@@ -1312,67 +1346,70 @@
         <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>19600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-18800</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-22100</v>
+        <v>-18700</v>
       </c>
       <c r="E21" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="K21" s="3">
         <v>-21300</v>
       </c>
-      <c r="F21" s="3">
-        <v>-30100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-13100</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-40000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-20500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-21300</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-20000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-14200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-18200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-15800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1382,8 +1419,11 @@
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1396,35 +1436,35 @@
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>300</v>
-      </c>
-      <c r="N22" s="3">
-        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1435,61 +1475,67 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-33100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-21100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-21900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-17200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>19300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20100</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1506,19 +1552,19 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
@@ -1527,7 +1573,7 @@
         <v>100</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1541,8 +1587,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-24800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-33100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-40700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-21100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-21800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-19600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-20100</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-33100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-40700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-21100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-21800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-19600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20100</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,34 +1979,37 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3400</v>
+        <v>2600</v>
       </c>
       <c r="E32" s="3">
-        <v>-6800</v>
+        <v>1800</v>
       </c>
       <c r="F32" s="3">
-        <v>-700</v>
+        <v>4800</v>
       </c>
       <c r="G32" s="3">
-        <v>-10800</v>
+        <v>-1700</v>
       </c>
       <c r="H32" s="3">
-        <v>8700</v>
+        <v>8000</v>
       </c>
       <c r="I32" s="3">
-        <v>-3700</v>
+        <v>-11400</v>
       </c>
       <c r="J32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-6300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
@@ -1948,78 +2018,84 @@
         <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-19600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>18800</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-33100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-40700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-21100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-21800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-19600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20100</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-33100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-40700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-21100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-21800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-19600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20100</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44829</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44738</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44647</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,61 +2310,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E41" s="3">
         <v>113000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>141000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>167900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>199900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>215900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>236000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>265200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q41" s="3">
         <v>1200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2330,49 +2420,52 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E43" s="3">
         <v>2400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9800</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2383,49 +2476,52 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E44" s="3">
         <v>34100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>35100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>32100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>32800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>32200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>31100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>29200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>33600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>25800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>17700</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2436,137 +2532,146 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E45" s="3">
         <v>2000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K45" s="3">
+        <v>4600</v>
+      </c>
+      <c r="L45" s="3">
+        <v>100900</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="G45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>4600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>100900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
-      </c>
-      <c r="R45" s="3">
-        <v>600</v>
       </c>
       <c r="S45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>127400</v>
+      </c>
+      <c r="E46" s="3">
         <v>151500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>182400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>210700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>239900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>255900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>272800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>301900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>140500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>39400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>42400</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q46" s="3">
         <v>1700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2584,60 +2689,63 @@
         <v>0</v>
       </c>
       <c r="P47" s="3">
-        <v>400200</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="3">
         <v>400200</v>
       </c>
       <c r="R47" s="3">
+        <v>400200</v>
+      </c>
+      <c r="S47" s="3">
         <v>400100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E48" s="3">
         <v>38000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39200</v>
       </c>
-      <c r="F48" s="3">
-        <v>39600</v>
-      </c>
       <c r="G48" s="3">
+        <v>25200</v>
+      </c>
+      <c r="H48" s="3">
         <v>39900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>38200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22700</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -2648,49 +2756,52 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E49" s="3">
         <v>9500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9600</v>
       </c>
-      <c r="F49" s="3">
-        <v>9700</v>
-      </c>
       <c r="G49" s="3">
+        <v>24100</v>
+      </c>
+      <c r="H49" s="3">
         <v>9800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10500</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,49 +2924,52 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5900</v>
+        <v>5600</v>
       </c>
       <c r="E52" s="3">
         <v>5900</v>
       </c>
       <c r="F52" s="3">
-        <v>6200</v>
+        <v>5900</v>
       </c>
       <c r="G52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H52" s="3">
         <v>6300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>178300</v>
+      </c>
+      <c r="E54" s="3">
         <v>204900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>237100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>266100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>295900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>310500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>325800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>351800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>182400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>76900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>75800</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q54" s="3">
         <v>401900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>402200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>402300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,44 +3138,45 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E57" s="3">
         <v>19800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27500</v>
       </c>
-      <c r="F57" s="3">
-        <v>26300</v>
-      </c>
       <c r="G57" s="3">
+        <v>23900</v>
+      </c>
+      <c r="H57" s="3">
         <v>25500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11400</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3061,31 +3192,34 @@
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3094,16 +3228,16 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>12300</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3114,137 +3248,146 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>19000</v>
+        <v>3200</v>
       </c>
       <c r="E59" s="3">
-        <v>16700</v>
+        <v>3400</v>
       </c>
       <c r="F59" s="3">
-        <v>20000</v>
+        <v>4100</v>
       </c>
       <c r="G59" s="3">
-        <v>19900</v>
+        <v>6500</v>
       </c>
       <c r="H59" s="3">
-        <v>18400</v>
+        <v>5800</v>
       </c>
       <c r="I59" s="3">
-        <v>16700</v>
+        <v>5000</v>
       </c>
       <c r="J59" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K59" s="3">
         <v>21700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>116600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>29600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>47100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E60" s="3">
         <v>38800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>44100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>46300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>45400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>40800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>29100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>134300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>40700</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q60" s="3">
         <v>29600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>47100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3253,11 +3396,11 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>5800</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3273,49 +3416,52 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7100</v>
+        <v>3700</v>
       </c>
       <c r="E62" s="3">
-        <v>9200</v>
+        <v>6500</v>
       </c>
       <c r="F62" s="3">
-        <v>14000</v>
+        <v>8400</v>
       </c>
       <c r="G62" s="3">
-        <v>12000</v>
+        <v>13100</v>
       </c>
       <c r="H62" s="3">
-        <v>20500</v>
+        <v>11000</v>
       </c>
       <c r="I62" s="3">
-        <v>9200</v>
+        <v>19200</v>
       </c>
       <c r="J62" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K62" s="3">
         <v>10600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6300</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3">
-        <v>13100</v>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>13100</v>
@@ -3323,11 +3469,14 @@
       <c r="R62" s="3">
         <v>13100</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E66" s="3">
         <v>45900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>60300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>57400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>61300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>38300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>139900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="3">
         <v>42700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>60200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,35 +3942,38 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-203100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-180400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-155600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-132000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-98900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-84300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-43600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-22400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3812,20 +3986,23 @@
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-57900</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>137700</v>
+      </c>
+      <c r="E76" s="3">
         <v>159000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>183800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>205900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>238500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>249100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>287500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>306800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>42500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>37900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q76" s="3">
         <v>359200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>361400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>342100</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44829</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44738</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44647</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-33100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-40700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-21100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-21800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-19600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20100</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,50 +4419,51 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2700</v>
+        <v>1400</v>
       </c>
       <c r="E83" s="3">
-        <v>2300</v>
+        <v>700</v>
       </c>
       <c r="F83" s="3">
-        <v>3000</v>
+        <v>700</v>
       </c>
       <c r="G83" s="3">
+        <v>200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>900</v>
+      </c>
+      <c r="I83" s="3">
         <v>1400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
-        <v>700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>700</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1300</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -4274,8 +4473,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-26000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-22900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-27600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-24600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-25500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-26500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-18600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-22800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,50 +4833,51 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5200</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-3200</v>
       </c>
       <c r="L91" s="3">
         <v>-3200</v>
       </c>
       <c r="M91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-2500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3800</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -4666,8 +4887,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,50 +4999,53 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5200</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-3200</v>
       </c>
       <c r="L94" s="3">
         <v>-3200</v>
       </c>
       <c r="M94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="N94" s="3">
         <v>-2500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3800</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -4825,8 +5055,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,31 +5079,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,50 +5301,53 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1600</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
         <v>193700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>126600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>15300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>30700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>24100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>18700</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -5111,31 +5357,34 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5164,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-28000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-26900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-32000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-20200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-29200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>163100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>96800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>LVWR</t>
   </si>
@@ -656,140 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44829</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44738</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44647</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E8" s="3">
         <v>4400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7000</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
@@ -799,53 +802,56 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E9" s="3">
         <v>6000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
@@ -855,53 +861,56 @@
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-4100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-5200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-2900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
@@ -911,8 +920,11 @@
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,13 +945,14 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>4</v>
+      <c r="D12" s="3">
+        <v>41700</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
@@ -947,12 +960,12 @@
       <c r="F12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="3">
         <v>54100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>4</v>
       </c>
@@ -989,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,17 +1061,20 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E14" s="3">
         <v>2500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1071,8 +1090,8 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1089,46 +1108,49 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2700</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="3">
         <v>2700</v>
       </c>
       <c r="F15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G15" s="3">
         <v>2300</v>
       </c>
-      <c r="G15" s="3">
-        <v>3000</v>
-      </c>
       <c r="H15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I15" s="3">
         <v>1400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>700</v>
       </c>
       <c r="J15" s="3">
         <v>700</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1157,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E17" s="3">
         <v>28400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>48800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>33500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>32700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>35700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-28200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-30400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-33800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-25300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-32000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-24900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-28200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-21000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1200</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,37 +1342,38 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
@@ -1349,70 +1382,73 @@
         <v>100</v>
       </c>
       <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>19600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-18800</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-18700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-23700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-23300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-32400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-15900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-42700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-23200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-21300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-20000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-14200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-18200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-15800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1422,8 +1458,11 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1448,26 +1487,26 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>300</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
       </c>
       <c r="Q22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1478,64 +1517,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-33100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-40700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-21100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-21900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-20900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>19300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-20100</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1555,19 +1600,19 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
@@ -1576,7 +1621,7 @@
         <v>100</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1590,8 +1635,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-22700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-33100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-40700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-21100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-21800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-19600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-20100</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-22700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-33100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-40700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-21100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-21800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-20100</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,37 +2048,40 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
@@ -2021,81 +2090,87 @@
         <v>-100</v>
       </c>
       <c r="O32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>1800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-19600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>18800</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-22700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-33100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-40700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-21100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-21800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20100</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-22700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-33100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-40700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-21100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-21800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20100</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44829</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44738</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44647</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,64 +2396,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E41" s="3">
         <v>88400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>113000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>141000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>167900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>199900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>215900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>236000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>265200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="3">
         <v>1200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1700</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,52 +2512,55 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E43" s="3">
         <v>2200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2479,52 +2571,55 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E44" s="3">
         <v>33400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>34100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>35100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>32100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>32800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>32200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>31100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>29200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>33600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>25800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>17700</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2535,120 +2630,129 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>3400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3000</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
-      </c>
-      <c r="S45" s="3">
-        <v>600</v>
       </c>
       <c r="T45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>98400</v>
+      </c>
+      <c r="E46" s="3">
         <v>127400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>151500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>182400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>210700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>239900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>255900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>272800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>301900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>140500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>39400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R46" s="3">
         <v>1700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2673,8 +2777,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2692,63 +2796,66 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3">
-        <v>400200</v>
+        <v>0</v>
       </c>
       <c r="R47" s="3">
         <v>400200</v>
       </c>
       <c r="S47" s="3">
+        <v>400200</v>
+      </c>
+      <c r="T47" s="3">
         <v>400100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E48" s="3">
         <v>35800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>39200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>39900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22700</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -2759,52 +2866,55 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E49" s="3">
         <v>9400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>24100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10500</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -2815,8 +2925,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,52 +3043,55 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>900</v>
+      </c>
+      <c r="E52" s="3">
         <v>5600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>5900</v>
       </c>
       <c r="F52" s="3">
         <v>5900</v>
       </c>
       <c r="G52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H52" s="3">
         <v>4900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -2983,8 +3102,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E54" s="3">
         <v>178300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>204900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>237100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>266100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>295900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>310500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>325800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>351800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>182400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>76900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>75800</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" s="3">
         <v>401900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>402200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>402300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,47 +3268,48 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E57" s="3">
         <v>16400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>25500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3195,25 +3325,28 @@
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1200</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1400</v>
       </c>
       <c r="I58" s="3">
         <v>1400</v>
@@ -3222,7 +3355,7 @@
         <v>1400</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3231,16 +3364,16 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>12300</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3251,147 +3384,156 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E59" s="3">
         <v>3200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>116600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>29600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>27600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>47100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E60" s="3">
         <v>35900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>44100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>46300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>45400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>40800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>134300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40700</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3">
         <v>29600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>47100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>400</v>
+      </c>
+      <c r="E61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3399,11 +3541,11 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>5800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3419,52 +3561,55 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E62" s="3">
         <v>3700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8400</v>
       </c>
-      <c r="G62" s="3">
-        <v>13100</v>
-      </c>
       <c r="H62" s="3">
+        <v>12900</v>
+      </c>
+      <c r="I62" s="3">
         <v>11000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6300</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3">
-        <v>13100</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R62" s="3">
         <v>13100</v>
@@ -3472,11 +3617,14 @@
       <c r="S62" s="3">
         <v>13100</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E66" s="3">
         <v>40600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>60300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>57400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>61300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>38300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>139900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" s="3">
         <v>42700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>40700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>60200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,38 +4115,41 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-225900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-203100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-180400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-155600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-132000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-98900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-84300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-43600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-22400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3989,20 +4162,23 @@
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>-3000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-57900</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E76" s="3">
         <v>137700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>159000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>183800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>205900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>238500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>249100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>287500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>306800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>42500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R76" s="3">
         <v>359200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>361400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>342100</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44829</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44738</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44647</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-22700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-33100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-40700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-21100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-21800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20100</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,53 +4617,54 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E83" s="3">
         <v>1400</v>
-      </c>
-      <c r="E83" s="3">
-        <v>700</v>
       </c>
       <c r="F83" s="3">
         <v>700</v>
       </c>
       <c r="G83" s="3">
+        <v>700</v>
+      </c>
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1300</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -4476,8 +4674,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-23100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-26000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-22900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-16600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-24600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-25500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-26500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-18600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-22800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,53 +5053,54 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5200</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-3200</v>
       </c>
       <c r="M91" s="3">
         <v>-3200</v>
       </c>
       <c r="N91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="O91" s="3">
         <v>-2500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -4890,8 +5110,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,53 +5228,56 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5200</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-3200</v>
       </c>
       <c r="M94" s="3">
         <v>-3200</v>
       </c>
       <c r="N94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="O94" s="3">
         <v>-2500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -5058,8 +5287,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5106,8 +5339,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5136,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,53 +5546,56 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1600</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3">
         <v>193700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>126600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>15300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>30700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>24100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>18700</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
@@ -5360,8 +5605,11 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5386,8 +5634,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5416,60 +5664,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-24600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-28000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-26900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-32000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-20200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-29200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>163100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>96800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>LVWR</t>
   </si>
@@ -656,146 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44829</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44738</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44647</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E8" s="3">
         <v>10800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7000</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
@@ -805,56 +809,59 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E9" s="3">
         <v>16100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8800</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
@@ -864,56 +871,59 @@
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E10" s="3">
         <v>-5400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-4100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-5200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-2900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-1800</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
@@ -923,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,29 +959,30 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3">
         <v>41700</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3">
         <v>54100</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,20 +1081,23 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>-900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1093,8 +1113,8 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1111,49 +1131,52 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
         <v>1000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E15" s="3">
         <v>1300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2700</v>
       </c>
       <c r="F15" s="3">
         <v>2700</v>
       </c>
       <c r="G15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H15" s="3">
         <v>2300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>700</v>
       </c>
       <c r="K15" s="3">
         <v>700</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E17" s="3">
         <v>36900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>48800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>33500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>39000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>35700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>31900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>32800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1200</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-26200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-24000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-28200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-30400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-33800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-25300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-32000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-28200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-21000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-19400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-17100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1200</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,40 +1376,41 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>11400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
@@ -1385,73 +1419,76 @@
         <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>19600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-18800</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-23200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-18700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-23700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-23300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-33300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-42700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-23200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-21300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-20000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-17900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-14200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1461,8 +1498,11 @@
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1490,26 +1530,26 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>300</v>
-      </c>
-      <c r="P22" s="3">
-        <v>100</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
       </c>
       <c r="R22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1520,67 +1560,73 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-22700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-23600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-33100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-40700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-21100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-17200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>19300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-20100</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1603,19 +1649,19 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
@@ -1624,7 +1670,7 @@
         <v>100</v>
       </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1638,8 +1684,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-22800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-22700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-24800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-33100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-40700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-21100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-16000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-20100</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-22800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-22700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-24800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-33100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-40700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-21100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-21800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-16000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-20100</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,40 +2118,43 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-11400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
@@ -2093,84 +2163,90 @@
         <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-19600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>18800</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-22800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-22700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-33100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-40700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-21100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-21800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-16000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-20100</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-22800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-22700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-33100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-40700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-21100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-21800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-16000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-20100</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44829</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44738</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44647</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,67 +2483,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E41" s="3">
         <v>64400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>88400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>113000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>141000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>167900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>199900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>215900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>236000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>265200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S41" s="3">
         <v>1200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2515,55 +2605,58 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E43" s="3">
         <v>4300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9800</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -2574,55 +2667,58 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E44" s="3">
         <v>26900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>33400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>34100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>35100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>32100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>32800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>32200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>31100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>29200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>33600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>25800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>17700</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -2633,126 +2729,135 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>100900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
-      </c>
-      <c r="T45" s="3">
-        <v>600</v>
       </c>
       <c r="U45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>81600</v>
+      </c>
+      <c r="E46" s="3">
         <v>98400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>127400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>151500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>182400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>210700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>239900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>255900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>272800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>301900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>140500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>42400</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S46" s="3">
         <v>1700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2780,8 +2885,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2799,66 +2904,69 @@
         <v>0</v>
       </c>
       <c r="R47" s="3">
-        <v>400200</v>
+        <v>0</v>
       </c>
       <c r="S47" s="3">
         <v>400200</v>
       </c>
       <c r="T47" s="3">
+        <v>400200</v>
+      </c>
+      <c r="U47" s="3">
         <v>400100</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E48" s="3">
         <v>22700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>35800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>39200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>39900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>38200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22700</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -2869,55 +2977,58 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E49" s="3">
         <v>21500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>24100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10500</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,55 +3163,58 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E52" s="3">
         <v>900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>5900</v>
       </c>
       <c r="G52" s="3">
         <v>5900</v>
       </c>
       <c r="H52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="I52" s="3">
         <v>4900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>128300</v>
+      </c>
+      <c r="E54" s="3">
         <v>148000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>178300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>204900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>237100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>266100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>295900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>310500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>325800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>351800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>182400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>76900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>75800</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S54" s="3">
         <v>401900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>402200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>402300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,50 +3399,51 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E57" s="3">
         <v>11500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>25500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11400</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3328,8 +3459,11 @@
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3337,19 +3471,19 @@
         <v>400</v>
       </c>
       <c r="E58" s="3">
+        <v>400</v>
+      </c>
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1400</v>
       </c>
       <c r="J58" s="3">
         <v>1400</v>
@@ -3358,7 +3492,7 @@
         <v>1400</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3367,16 +3501,16 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>12300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3387,156 +3521,165 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
         <v>3700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>116600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17000</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S59" s="3">
         <v>29600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>27600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>47100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E60" s="3">
         <v>29900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>35900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>44100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>46300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>45400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>40800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>34400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>134300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>40700</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S60" s="3">
         <v>29600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>47100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>800</v>
+      </c>
+      <c r="E61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3544,11 +3687,11 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>5800</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3564,55 +3707,58 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E62" s="3">
         <v>2100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>19200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6300</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R62" s="3">
-        <v>13100</v>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S62" s="3">
         <v>13100</v>
@@ -3620,11 +3766,14 @@
       <c r="T62" s="3">
         <v>13100</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E66" s="3">
         <v>32800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>40600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>60300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>61300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>45000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>139900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>39000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52800</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S66" s="3">
         <v>42700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>40700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>60200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,41 +4289,44 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-245200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-225900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-203100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-180400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-155600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-132000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-98900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-84300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-43600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-22400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4165,20 +4339,23 @@
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S72" s="3">
         <v>-3000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-57900</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>97200</v>
+      </c>
+      <c r="E76" s="3">
         <v>115100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>137700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>159000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>183800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>205900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>238500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>249100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>287500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>306800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>42500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S76" s="3">
         <v>359200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>361400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>342100</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44829</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44738</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44647</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-22800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-22700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-33100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-40700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-21100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-21800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-16000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-20100</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,56 +4816,57 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>700</v>
       </c>
       <c r="G83" s="3">
         <v>700</v>
       </c>
       <c r="H83" s="3">
+        <v>700</v>
+      </c>
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1300</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -4677,8 +4876,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-21900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-23100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-26000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-22900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-27600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-16600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-24600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-25500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-26500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-18600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-19000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,56 +5274,57 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-3200</v>
       </c>
       <c r="N91" s="3">
         <v>-3200</v>
       </c>
       <c r="O91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="P91" s="3">
         <v>-2500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3800</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -5113,8 +5334,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,56 +5458,59 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5200</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-3200</v>
       </c>
       <c r="N94" s="3">
         <v>-3200</v>
       </c>
       <c r="O94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="P94" s="3">
         <v>-2500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3800</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -5290,8 +5520,11 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5342,8 +5576,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,56 +5792,59 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1600</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
         <v>193700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>126600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>15300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>30700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>24100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>18700</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -5608,8 +5854,11 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5637,8 +5886,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5667,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-24000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-24600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-28000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-26900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-32000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-20200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-29200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>163100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>96800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>LVWR</t>
   </si>
@@ -656,153 +656,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44829</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44647</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7000</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
@@ -812,59 +816,62 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E9" s="3">
         <v>4900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
@@ -874,59 +881,62 @@
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-5400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-1800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-4100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-5200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-2900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-1800</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
@@ -936,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,32 +973,33 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3">
         <v>41700</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="3">
         <v>54100</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,23 +1101,26 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>-900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1116,8 +1136,8 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1134,52 +1154,55 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="3">
         <v>1000</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E15" s="3">
         <v>3100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2700</v>
       </c>
       <c r="G15" s="3">
         <v>2700</v>
       </c>
       <c r="H15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I15" s="3">
         <v>2300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>700</v>
       </c>
       <c r="L15" s="3">
         <v>700</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E17" s="3">
         <v>23400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>36900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>35400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>48800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>33500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>39000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>32700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>35700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>31900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1200</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-26200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-24000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-28200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-33800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-25300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-32000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-28200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1200</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,43 +1410,44 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
@@ -1422,76 +1456,79 @@
         <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>19600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-18800</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-16700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-23200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-23700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-23300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-33300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-42700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-23200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-21300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-20000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-17900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-18200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-15800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1501,8 +1538,11 @@
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1533,26 +1573,26 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>300</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>100</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
       </c>
       <c r="S22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1563,70 +1603,76 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-22800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-22700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-23600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-33100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-40700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>19300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-20100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1652,19 +1698,19 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3">
         <v>100</v>
@@ -1673,7 +1719,7 @@
         <v>100</v>
       </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1687,8 +1733,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-22800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-22700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-24800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-23600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-33100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-40700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>19300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-20100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-22800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-22700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-23600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-33100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-40700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-21100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>19300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-20100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,43 +2188,46 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
@@ -2166,87 +2236,93 @@
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-19600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>18800</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-22800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-22700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-23600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-33100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-40700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-21100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>19300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-20100</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-22800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-22700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-23600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-33100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-40700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-21100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>19300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-20100</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44829</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44647</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E41" s="3">
         <v>46200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>64400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>88400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>113000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>141000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>167900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>199900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>215900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>236000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>265200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T41" s="3">
         <v>1200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,58 +2698,61 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E43" s="3">
         <v>3600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9800</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -2670,58 +2763,61 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E44" s="3">
         <v>28500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>33400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>34100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>35100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>32100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>32800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>32200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>31100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>29200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>33600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>25800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>17700</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -2732,132 +2828,141 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E45" s="3">
         <v>3300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3000</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>500</v>
-      </c>
-      <c r="U45" s="3">
-        <v>600</v>
       </c>
       <c r="V45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E46" s="3">
         <v>81600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>98400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>127400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>151500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>182400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>210700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>239900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>255900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>272800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>301900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>140500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>39400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>42400</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T46" s="3">
         <v>1700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2888,8 +2993,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2907,69 +3012,72 @@
         <v>0</v>
       </c>
       <c r="S47" s="3">
-        <v>400200</v>
+        <v>0</v>
       </c>
       <c r="T47" s="3">
         <v>400200</v>
       </c>
       <c r="U47" s="3">
+        <v>400200</v>
+      </c>
+      <c r="V47" s="3">
         <v>400100</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E48" s="3">
         <v>32500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>39200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>39900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>38200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -2980,8 +3088,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2989,49 +3100,49 @@
         <v>9300</v>
       </c>
       <c r="E49" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F49" s="3">
         <v>21500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10500</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,58 +3283,61 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E52" s="3">
         <v>4800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>5900</v>
       </c>
       <c r="H52" s="3">
         <v>5900</v>
       </c>
       <c r="I52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J52" s="3">
         <v>4900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>109800</v>
+      </c>
+      <c r="E54" s="3">
         <v>128300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>148000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>178300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>204900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>237100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>266100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>295900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>310500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>325800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>351800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>182400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>76900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>75800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T54" s="3">
         <v>401900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>402200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>402300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,53 +3530,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E57" s="3">
         <v>16900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>25500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11400</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3462,31 +3593,34 @@
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
       </c>
       <c r="F58" s="3">
+        <v>400</v>
+      </c>
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1400</v>
       </c>
       <c r="K58" s="3">
         <v>1400</v>
@@ -3495,7 +3629,7 @@
         <v>1400</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3504,16 +3638,16 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>12300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -3524,165 +3658,174 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>3700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>116600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3">
         <v>29600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>27600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>47100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E60" s="3">
         <v>28600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>38800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>44100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>46300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>45400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>134300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>40700</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T60" s="3">
         <v>29600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>27600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>47100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>600</v>
+      </c>
+      <c r="E61" s="3">
         <v>800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3690,11 +3833,11 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>5800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3710,58 +3853,61 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6300</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S62" s="3">
-        <v>13100</v>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T62" s="3">
         <v>13100</v>
@@ -3769,11 +3915,14 @@
       <c r="U62" s="3">
         <v>13100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E66" s="3">
         <v>31100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>40600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>60300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>57400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>61300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>45000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>139900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T66" s="3">
         <v>42700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>40700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>60200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,44 +4463,47 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-264000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-245200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-225900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-203100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-180400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-155600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-132000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-98900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-84300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-43600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-22400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4342,20 +4516,23 @@
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T72" s="3">
         <v>-3000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-57900</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>79700</v>
+      </c>
+      <c r="E76" s="3">
         <v>97200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>115100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>137700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>159000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>183800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>205900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>238500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>249100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>287500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>306800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>42500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T76" s="3">
         <v>359200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>361400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>342100</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44829</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44647</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-22800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-22700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-23600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-33100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-40700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-21100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>19300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-20100</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,59 +5015,60 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E83" s="3">
         <v>2300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>700</v>
       </c>
       <c r="H83" s="3">
         <v>700</v>
       </c>
       <c r="I83" s="3">
+        <v>700</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1300</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-21900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-26000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-22900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-27600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-16600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-25500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-26500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-18600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-22800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,59 +5495,60 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-3200</v>
       </c>
       <c r="O91" s="3">
         <v>-3200</v>
       </c>
       <c r="P91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3800</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,59 +5688,62 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5200</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-3200</v>
       </c>
       <c r="O94" s="3">
         <v>-3200</v>
       </c>
       <c r="P94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3800</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -5523,8 +5753,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5579,8 +5813,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,59 +6038,62 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1600</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3">
         <v>193700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>126600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>15300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>30700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>24100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>18700</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -5857,8 +6103,11 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5889,8 +6138,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5919,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-24000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-24600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-26900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-32000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-29200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>163100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>96800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>LVWR</t>
   </si>
@@ -656,167 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44829</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44738</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44647</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E8" s="3">
         <v>5700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7000</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
@@ -826,65 +829,68 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E9" s="3">
         <v>8600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
@@ -894,65 +900,68 @@
       <c r="X9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-2200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-5400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-1500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-1800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-4100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-5200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-2900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-1800</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
@@ -962,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,13 +1000,14 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>4</v>
+      <c r="D12" s="3">
+        <v>23900</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
@@ -1002,24 +1015,24 @@
       <c r="F12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="3">
         <v>41700</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3">
         <v>54100</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1056,8 +1069,11 @@
       <c r="X12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1140,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1138,15 +1157,15 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>-900</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I14" s="3">
         <v>2100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1162,8 +1181,8 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1180,58 +1199,61 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3">
         <v>1000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E15" s="3">
         <v>2400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>2700</v>
       </c>
       <c r="I15" s="3">
         <v>2700</v>
       </c>
       <c r="J15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K15" s="3">
         <v>2300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1400</v>
-      </c>
-      <c r="M15" s="3">
-        <v>700</v>
       </c>
       <c r="N15" s="3">
         <v>700</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1260,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E17" s="3">
         <v>24500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23400</v>
       </c>
-      <c r="G17" s="3">
-        <v>36900</v>
-      </c>
       <c r="H17" s="3">
+        <v>36100</v>
+      </c>
+      <c r="I17" s="3">
         <v>28800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>35400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>48800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>33500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>39000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>31900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>32800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1200</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-18300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-20700</v>
       </c>
-      <c r="G18" s="3">
-        <v>-26200</v>
-      </c>
       <c r="H18" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-24400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-30400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-25300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-32000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-28200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-19900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-17100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1200</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,49 +1477,50 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6300</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
@@ -1496,82 +1529,85 @@
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>19600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-18800</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-17100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-16600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="O21" s="3">
         <v>-23200</v>
       </c>
-      <c r="H21" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-23700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-23300</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-33300</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-15900</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-42700</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-23200</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-21300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-14200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-18200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-15800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1581,13 +1617,16 @@
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>300</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>4</v>
@@ -1619,26 +1658,26 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>300</v>
-      </c>
-      <c r="S22" s="3">
-        <v>100</v>
       </c>
       <c r="T22" s="3">
         <v>100</v>
       </c>
       <c r="U22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1649,76 +1688,82 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-22800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-22700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-33100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-40700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-19700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-17200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>19300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-20100</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1726,7 +1771,7 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1750,19 +1795,19 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
@@ -1771,7 +1816,7 @@
         <v>100</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1785,8 +1830,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-18800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-22800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-22700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-24800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-33100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-40700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-16000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-19800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-17200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-20100</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-22800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-22700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-24800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-33100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-40700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-16000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-19800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-17200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-20100</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,49 +2327,52 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6300</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
@@ -2312,93 +2381,99 @@
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-19600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>18800</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-22800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-22700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-24800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-33100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-40700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-16000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-19800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-20100</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-22800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-22700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-24800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-33100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-40700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-16000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-19800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-20100</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44829</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44738</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44647</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,76 +2743,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E41" s="3">
         <v>16300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>29300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>46200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>64400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>88400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>113000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>141000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>167900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>199900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>215900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>236000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>265200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11900</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V41" s="3">
         <v>1200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1700</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,64 +2883,67 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9800</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2862,64 +2954,67 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E44" s="3">
         <v>22900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>27600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>28500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>26900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>33400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>34100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>35100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>32100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>32800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>32200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>31100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>29200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>33600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>25800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>17700</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -2930,144 +3025,153 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3600</v>
+        <v>800</v>
       </c>
       <c r="E45" s="3">
         <v>3600</v>
       </c>
       <c r="F45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G45" s="3">
         <v>3300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>100900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
-      </c>
-      <c r="W45" s="3">
-        <v>600</v>
       </c>
       <c r="X45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E46" s="3">
         <v>46300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>64900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>81600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>98400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>127400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>151500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>182400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>210700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>239900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>255900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>272800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>301900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>140500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>39400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>42400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V46" s="3">
         <v>1700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3104,8 +3208,8 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3123,75 +3227,78 @@
         <v>0</v>
       </c>
       <c r="U47" s="3">
-        <v>400200</v>
+        <v>0</v>
       </c>
       <c r="V47" s="3">
         <v>400200</v>
       </c>
       <c r="W47" s="3">
+        <v>400200</v>
+      </c>
+      <c r="X47" s="3">
         <v>400100</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E48" s="3">
         <v>29500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>39200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>39900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>36100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>22700</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3202,64 +3309,67 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E49" s="3">
         <v>9200</v>
-      </c>
-      <c r="E49" s="3">
-        <v>9300</v>
       </c>
       <c r="F49" s="3">
         <v>9300</v>
       </c>
       <c r="G49" s="3">
+        <v>9300</v>
+      </c>
+      <c r="H49" s="3">
         <v>21500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>24100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10500</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3270,8 +3380,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,64 +3522,67 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4800</v>
       </c>
-      <c r="G52" s="3">
-        <v>900</v>
-      </c>
       <c r="H52" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I52" s="3">
         <v>5600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>5900</v>
       </c>
       <c r="J52" s="3">
         <v>5900</v>
       </c>
       <c r="K52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="L52" s="3">
         <v>4900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3474,8 +3593,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3664,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>146400</v>
+      </c>
+      <c r="E54" s="3">
         <v>89200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>109800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>128300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>148000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>178300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>204900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>237100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>266100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>295900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>310500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>325800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>351800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>182400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>76900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>75800</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V54" s="3">
         <v>401900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>402200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>402300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,59 +3791,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E57" s="3">
         <v>10000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>27500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>25500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>18500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11400</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3730,37 +3860,40 @@
       <c r="X57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>400</v>
       </c>
       <c r="G58" s="3">
         <v>400</v>
       </c>
       <c r="H58" s="3">
+        <v>400</v>
+      </c>
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1400</v>
       </c>
       <c r="M58" s="3">
         <v>1400</v>
@@ -3769,7 +3902,7 @@
         <v>1400</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -3778,16 +3911,16 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>12300</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3798,183 +3931,192 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
         <v>3700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>116600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3">
         <v>29600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>27600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>47100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E60" s="3">
         <v>24100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>38800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>44100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>46300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>45400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>40800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>34400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>134300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>33100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>40700</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V60" s="3">
         <v>29600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>27600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>47100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3982,11 +4124,11 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>5800</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4002,64 +4144,67 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E62" s="3">
         <v>2500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>19200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6300</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>13100</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V62" s="3">
         <v>13100</v>
@@ -4067,11 +4212,14 @@
       <c r="W62" s="3">
         <v>13100</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4428,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>100400</v>
+      </c>
+      <c r="E66" s="3">
         <v>27400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>30100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>40600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>60300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>61300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>139900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>52800</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V66" s="3">
         <v>42700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>40700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>60200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,50 +4810,53 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-301000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-283400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-264000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-245200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-225900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-203100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-180400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-155600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-132000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-98900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-84300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-43600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-22400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4696,20 +4869,23 @@
       <c r="T72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V72" s="3">
         <v>-3000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-57900</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5094,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E76" s="3">
         <v>61800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>79700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>97200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>115100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>137700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>159000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>183800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>205900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>238500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>249100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>287500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>306800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>42500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>37900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V76" s="3">
         <v>359200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>361400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>342100</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44829</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44738</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44647</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-22800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-22700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-24800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-33100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-40700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-16000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-19800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-20100</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,65 +5412,66 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2700</v>
+        <v>1100</v>
       </c>
       <c r="E83" s="3">
         <v>2700</v>
       </c>
       <c r="F83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G83" s="3">
         <v>2300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>700</v>
       </c>
       <c r="J83" s="3">
         <v>700</v>
       </c>
       <c r="K83" s="3">
+        <v>700</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1300</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
@@ -5283,8 +5481,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-17500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-21900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-23100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-26000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-22900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-27600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-16600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-24600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-19000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-22800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-15300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-700</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,65 +5936,66 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5200</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-3200</v>
       </c>
       <c r="Q91" s="3">
         <v>-3200</v>
       </c>
       <c r="R91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="S91" s="3">
         <v>-2500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3800</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -5785,8 +6005,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,65 +6147,68 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5200</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-3200</v>
       </c>
       <c r="Q94" s="3">
         <v>-3200</v>
       </c>
       <c r="R94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="S94" s="3">
         <v>-2500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3800</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -5989,8 +6218,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6053,8 +6286,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,65 +6529,68 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-500</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3">
         <v>193700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>126600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>15300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>30700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>24100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>18700</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -6355,17 +6600,20 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F101" s="3" t="s">
         <v>4</v>
       </c>
@@ -6393,8 +6641,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6423,72 +6671,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>66500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-24000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-24600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-28000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-26900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-32000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-20200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-29200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>163100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>96800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LVWR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>LVWR</t>
   </si>
@@ -656,173 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44829</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44647</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E8" s="3">
         <v>11400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7000</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
@@ -832,68 +836,71 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E9" s="3">
         <v>11300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>20300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8800</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
@@ -903,68 +910,71 @@
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-2900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-2200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-5400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-1500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-1800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-4100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-5200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-2900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-1800</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
@@ -974,8 +984,11 @@
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,41 +1014,42 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3">
         <v>23900</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3">
         <v>41700</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3">
         <v>54100</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1072,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,8 +1160,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1160,15 +1180,15 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1184,8 +1204,8 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1202,61 +1222,64 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E15" s="3">
         <v>1100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2700</v>
       </c>
       <c r="J15" s="3">
         <v>2700</v>
       </c>
       <c r="K15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L15" s="3">
         <v>2300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1400</v>
-      </c>
-      <c r="N15" s="3">
-        <v>700</v>
       </c>
       <c r="O15" s="3">
         <v>700</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1285,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,79 +1335,83 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E17" s="3">
         <v>29100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>36100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>48800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>33500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>31900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>32800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>24100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1200</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1389,70 +1419,73 @@
         <v>-17700</v>
       </c>
       <c r="E18" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-18800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-20700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-25300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-24400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-28200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-30400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-33800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-25300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-32000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-19400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-19900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-17100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,52 +1511,53 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>11400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
@@ -1532,85 +1566,88 @@
         <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>19600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-16300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-17100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-16700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-22300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-19100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-23700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-23300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-33300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-42700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-23200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-20000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-17900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-14200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-18200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-15800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1620,17 +1657,20 @@
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1661,26 +1701,26 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>300</v>
-      </c>
-      <c r="T22" s="3">
-        <v>100</v>
       </c>
       <c r="U22" s="3">
         <v>100</v>
       </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1691,90 +1731,96 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-19300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-22800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-22700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-33100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-40700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-19500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-19700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-17200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>19300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1798,19 +1844,19 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
@@ -1819,7 +1865,7 @@
         <v>100</v>
       </c>
       <c r="U24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1833,8 +1879,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-18800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-19300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-22800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-22700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-24800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-23600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-33100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-40700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-19600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-16000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-19800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-17200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-18800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-22800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-22700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-24800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-23600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-33100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-40700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-19600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-19800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-17200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,52 +2397,55 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-11400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
@@ -2384,96 +2454,102 @@
         <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-19600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>18800</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-18800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-22800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-22700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-24800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-23600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-33100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-40700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-19600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-16000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-19800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-18800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-22800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-22700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-24800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-23600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-33100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-40700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-19600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-16000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-19800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44829</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44647</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,79 +2830,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E41" s="3">
         <v>82800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>46200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>64400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>88400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>113000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>141000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>167900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>199900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>215900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>236000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>265200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11900</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W41" s="3">
         <v>1200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1700</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2886,67 +2976,70 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E43" s="3">
         <v>4000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9800</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -2957,67 +3050,70 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E44" s="3">
         <v>15300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>22900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>27600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>28500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>26900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>33400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>34100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>35100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>32100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>32800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>32200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>31100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>29200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>33600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>25800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>17700</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3028,150 +3124,159 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3600</v>
       </c>
       <c r="F45" s="3">
         <v>3600</v>
       </c>
       <c r="G45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H45" s="3">
         <v>3300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>100900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>500</v>
-      </c>
-      <c r="X45" s="3">
-        <v>600</v>
       </c>
       <c r="Y45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E46" s="3">
         <v>104900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>46300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>64900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>81600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>98400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>127400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>151500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>182400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>210700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>239900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>255900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>272800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>301900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>140500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>39400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>42400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W46" s="3">
         <v>1700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3211,8 +3316,8 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3230,78 +3335,81 @@
         <v>0</v>
       </c>
       <c r="V47" s="3">
-        <v>400200</v>
+        <v>0</v>
       </c>
       <c r="W47" s="3">
         <v>400200</v>
       </c>
       <c r="X47" s="3">
+        <v>400200</v>
+      </c>
+      <c r="Y47" s="3">
         <v>400100</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E48" s="3">
         <v>17100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>38000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>39200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>39900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>36100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22700</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3312,67 +3420,70 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E49" s="3">
         <v>20400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9200</v>
-      </c>
-      <c r="F49" s="3">
-        <v>9300</v>
       </c>
       <c r="G49" s="3">
         <v>9300</v>
       </c>
       <c r="H49" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I49" s="3">
         <v>21500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>24100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10500</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3383,8 +3494,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,67 +3642,70 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E52" s="3">
         <v>4000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>5900</v>
       </c>
       <c r="K52" s="3">
         <v>5900</v>
       </c>
       <c r="L52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="M52" s="3">
         <v>4900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3596,8 +3716,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>127600</v>
+      </c>
+      <c r="E54" s="3">
         <v>146400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>89200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>109800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>128300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>148000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>178300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>204900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>237100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>266100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>295900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>310500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>325800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>351800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>182400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>76900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>75800</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W54" s="3">
         <v>401900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>402200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>402300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,62 +3922,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E57" s="3">
         <v>9000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>27500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>23900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>25500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11400</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3863,40 +3994,43 @@
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>400</v>
       </c>
       <c r="H58" s="3">
         <v>400</v>
       </c>
       <c r="I58" s="3">
+        <v>400</v>
+      </c>
+      <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1200</v>
-      </c>
-      <c r="M58" s="3">
-        <v>1400</v>
       </c>
       <c r="N58" s="3">
         <v>1400</v>
@@ -3905,7 +4039,7 @@
         <v>1400</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3914,16 +4048,16 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>12300</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3934,192 +4068,201 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
         <v>3400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
         <v>3700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>116600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W59" s="3">
         <v>29600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>27600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>47100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E60" s="3">
         <v>22700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>24100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>44100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>46300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>45400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>34400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>134300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>33100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>40700</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W60" s="3">
         <v>29600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>27600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>47100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E61" s="3">
         <v>74400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4127,11 +4270,11 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>5800</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4147,67 +4290,70 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E62" s="3">
         <v>2700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>19200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6300</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V62" s="3">
-        <v>13100</v>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W62" s="3">
         <v>13100</v>
@@ -4215,11 +4361,14 @@
       <c r="X62" s="3">
         <v>13100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>99300</v>
+      </c>
+      <c r="E66" s="3">
         <v>100400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>40600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>60300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>57400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>61300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>139900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>39000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>52800</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W66" s="3">
         <v>42700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>40700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>60200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,53 +4984,56 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-319200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-301000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-283400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-264000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-245200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-225900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-203100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-180400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-155600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-132000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-98900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-84300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-43600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4872,20 +5046,23 @@
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W72" s="3">
         <v>-3000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-57900</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E76" s="3">
         <v>46000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>61800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>79700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>97200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>115100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>137700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>159000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>183800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>205900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>238500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>249100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>287500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>306800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>42500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>37900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W76" s="3">
         <v>359200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>361400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>342100</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44829</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44647</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-18800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-22800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-22700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-24800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-23600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-33100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-40700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-19600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-16000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-19800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,68 +5611,69 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E83" s="3">
         <v>1100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2700</v>
       </c>
       <c r="F83" s="3">
         <v>2700</v>
       </c>
       <c r="G83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H83" s="3">
         <v>2300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>700</v>
       </c>
       <c r="K83" s="3">
         <v>700</v>
       </c>
       <c r="L83" s="3">
+        <v>700</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1300</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
@@ -5484,8 +5683,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-17500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-23100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-27600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-16600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-24600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-26500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-19000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-22800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-15300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,68 +6157,69 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5200</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-3200</v>
       </c>
       <c r="R91" s="3">
         <v>-3200</v>
       </c>
       <c r="S91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="T91" s="3">
         <v>-2500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3800</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -6008,8 +6229,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,68 +6377,71 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5200</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-3200</v>
       </c>
       <c r="R94" s="3">
         <v>-3200</v>
       </c>
       <c r="S94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="T94" s="3">
         <v>-2500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3800</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
@@ -6221,8 +6451,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6289,8 +6523,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,68 +6775,71 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E100" s="3">
         <v>75500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-500</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1600</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3">
         <v>193700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>126600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>15300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>30700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>24100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>18700</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -6603,20 +6849,23 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G101" s="3" t="s">
         <v>4</v>
       </c>
@@ -6644,8 +6893,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6674,75 +6923,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E102" s="3">
         <v>66500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-24000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-24600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-32000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-20200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-29200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>163100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>96800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>
